--- a/experimental logs.xlsx
+++ b/experimental logs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23697\Desktop\Dilated_ResNet_phase_retrieval\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23697\Desktop\dilated-resnet-test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E9F46C8-93C5-451E-BADB-95175058779C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2250186C-FCC9-4516-8500-A3D6CC8BBFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="530" windowWidth="23890" windowHeight="14340" xr2:uid="{4D5B9836-5BBE-4ADA-8779-E1FDBE277735}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
   <si>
     <t>实验编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -365,11 +365,18 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>加入不对称和非高斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>加入超高斯，50-230，F噪声</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>G1_G2_g_f_s</t>
+  </si>
+  <si>
+    <t>G1_G2_g_f_s_a</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上，加入不对称，sig_max=2.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -763,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E586A856-7FB1-484F-B2DE-DAA60C61488E}">
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J41"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
@@ -775,7 +782,7 @@
     <col min="7" max="7" width="8.4140625" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.4140625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="54.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="47.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
@@ -1872,18 +1879,27 @@
       <c r="A39" s="1">
         <v>38</v>
       </c>
+      <c r="B39" s="3" t="s">
+        <v>83</v>
+      </c>
       <c r="J39" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J47" t="s">
-        <v>82</v>
+      <c r="B40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="J40" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A41" s="1">
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/experimental logs.xlsx
+++ b/experimental logs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23697\Desktop\dilated-resnet-test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\23697\Desktop\Dilated_ResNet_phase_retrieval\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2250186C-FCC9-4516-8500-A3D6CC8BBFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC2B637B-AAB4-4097-A8C5-8B47720E47D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="600" yWindow="530" windowWidth="23890" windowHeight="14340" xr2:uid="{4D5B9836-5BBE-4ADA-8779-E1FDBE277735}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="87">
   <si>
     <t>实验编号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -377,6 +377,10 @@
   </si>
   <si>
     <t>同上，加入不对称，sig_max=2.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10000+80000</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1901,6 +1905,12 @@
       <c r="A41" s="1">
         <v>40</v>
       </c>
+      <c r="B41" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J41" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
